--- a/plot_Tutorial 2 barras.xlsx
+++ b/plot_Tutorial 2 barras.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="34">
   <si>
     <t>Ângulo</t>
   </si>
@@ -58,16 +58,13 @@
     <t>Modificado sem contingência</t>
   </si>
   <si>
-    <t>Modificado com contingência</t>
-  </si>
-  <si>
     <t>40.00</t>
   </si>
   <si>
     <t xml:space="preserve"> 4.27</t>
   </si>
   <si>
-    <t>48.93</t>
+    <t>57.86</t>
   </si>
   <si>
     <t>126.3</t>
@@ -88,7 +85,7 @@
     <t>-22.5</t>
   </si>
   <si>
-    <t>22.08</t>
+    <t>31.01</t>
   </si>
   <si>
     <t>99.49</t>
@@ -113,9 +110,6 @@
   </si>
   <si>
     <t>Violação de Tensão sem contingência</t>
-  </si>
-  <si>
-    <t>Violação de Tensão - Contingência 1 - Circuito da Barra 3 (BARRA-3) p/ Barra 2 (BARRA-2)</t>
   </si>
   <si>
     <t>Violação de Fluxo sem contingência</t>
@@ -493,25 +487,25 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>30</v>
-      </c>
-      <c r="I2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -522,16 +516,16 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -539,19 +533,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -562,16 +556,16 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -582,16 +576,16 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -602,16 +596,16 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -622,16 +616,16 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" t="s">
         <v>28</v>
       </c>
-      <c r="H8" t="s">
-        <v>29</v>
-      </c>
       <c r="I8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
